--- a/output/pdf_financials_xlsx/OGW.xlsx
+++ b/output/pdf_financials_xlsx/OGW.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="24">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="28">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="30">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.007212</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.007212</v>
       </c>
     </row>
     <row r="93">
@@ -2626,7 +2626,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.007212</v>
       </c>
@@ -4048,10 +4052,10 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3.300507</v>
+        <v>-3.300507</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>2.249857</v>
+        <v>-2.249857</v>
       </c>
     </row>
     <row r="69">

--- a/output/pdf_financials_xlsx/OGW.xlsx
+++ b/output/pdf_financials_xlsx/OGW.xlsx
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/OGW.xlsx
+++ b/output/pdf_financials_xlsx/OGW.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.180767</v>
+        <v>0.494767</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.093391</v>
+        <v>0.341724</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.515906</v>
+        <v>0.829906</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.008025</v>
+        <v>1.256358</v>
       </c>
     </row>
     <row r="11">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011075</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020852</v>
       </c>
     </row>
     <row r="102">
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.042771</v>
+        <v>-0.053846</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.482606</v>
+        <v>1.461754</v>
       </c>
     </row>
     <row r="107">
@@ -2916,7 +2916,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-0.011075</v>
       </c>
@@ -3024,7 +3028,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>3.841429</v>
       </c>
@@ -3730,7 +3738,11 @@
           <t>Management and director fees 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.314</v>
       </c>
